--- a/diseases/d168/2005-2009.xlsx
+++ b/diseases/d168/2005-2009.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN94" t="b">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -20052,7 +20052,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -22110,7 +22110,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -22796,7 +22796,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -23482,7 +23482,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -25395,7 +25395,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -26081,7 +26081,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -27453,7 +27453,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -28973,7 +28973,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -29807,7 +29807,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -30641,7 +30641,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -31475,7 +31475,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -32309,7 +32309,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -33143,7 +33143,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -34370,7 +34370,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -35204,7 +35204,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -36038,7 +36038,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -36872,7 +36872,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -38540,7 +38540,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -39374,7 +39374,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -41042,7 +41042,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -41876,7 +41876,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -42710,7 +42710,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN244" t="b">

--- a/diseases/d168/2005-2009.xlsx
+++ b/diseases/d168/2005-2009.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -17984,7 +17984,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20728,7 +20728,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -22786,7 +22786,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -24699,7 +24699,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -25385,7 +25385,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26071,7 +26071,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27443,7 +27443,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28963,7 +28963,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -29797,7 +29797,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30631,7 +30631,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -31465,7 +31465,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32299,7 +32299,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -33133,7 +33133,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34360,7 +34360,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -35194,7 +35194,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -36862,7 +36862,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -37696,7 +37696,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -38530,7 +38530,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -39364,7 +39364,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -40198,7 +40198,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -41032,7 +41032,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -41866,7 +41866,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
